--- a/data/trans_orig/PCS12_SP_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>612733</t>
+          <t>612280</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>673599</t>
+          <t>677562</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>966956</t>
+          <t>966191</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1025812</t>
+          <t>1025466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1596328</t>
+          <t>1592478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1685048</t>
+          <t>1687401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>358124</t>
+          <t>354161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418990</t>
+          <t>419443</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289301</t>
+          <t>289647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348157</t>
+          <t>348922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661787</t>
+          <t>659434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750507</t>
+          <t>754357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>534420</t>
+          <t>531527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>609492</t>
+          <t>610934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>682656</t>
+          <t>683709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>759262</t>
+          <t>760617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1230966</t>
+          <t>1234878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1346291</t>
+          <t>1347323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1083921</t>
+          <t>1082479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1158993</t>
+          <t>1161886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>828411</t>
+          <t>827056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>905017</t>
+          <t>903964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1934795</t>
+          <t>1933763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2050120</t>
+          <t>2046208</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>157228</t>
+          <t>156720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203491</t>
+          <t>202473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186433</t>
+          <t>187883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>231320</t>
+          <t>233104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>359595</t>
+          <t>356904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>424920</t>
+          <t>420836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>347917</t>
+          <t>348935</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>394180</t>
+          <t>394688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245092</t>
+          <t>243308</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>289979</t>
+          <t>288529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602900</t>
+          <t>606984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>668225</t>
+          <t>670916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1342788</t>
+          <t>1334686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1458215</t>
+          <t>1458948</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1870650</t>
+          <t>1865497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1988583</t>
+          <t>1982855</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3234788</t>
+          <t>3242413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3405160</t>
+          <t>3406066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1818328</t>
+          <t>1817595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1933755</t>
+          <t>1941857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1390614</t>
+          <t>1396342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1508547</t>
+          <t>1513700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3250581</t>
+          <t>3249675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3420953</t>
+          <t>3413328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>600141</t>
+          <t>601221</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>662767</t>
+          <t>659035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>950233</t>
+          <t>953302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1019060</t>
+          <t>1019602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1566604</t>
+          <t>1570548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1658602</t>
+          <t>1661291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,84%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>311876</t>
+          <t>315608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>374502</t>
+          <t>373422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>318737</t>
+          <t>318195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>387564</t>
+          <t>384495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>653838</t>
+          <t>651149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745836</t>
+          <t>741892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>688000</t>
+          <t>688590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>774469</t>
+          <t>778597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>726209</t>
+          <t>725513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>809361</t>
+          <t>810901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1439544</t>
+          <t>1440591</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1562283</t>
+          <t>1562730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1189488</t>
+          <t>1185360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1275957</t>
+          <t>1275367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>948442</t>
+          <t>946902</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1031594</t>
+          <t>1032290</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2159477</t>
+          <t>2159030</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2282216</t>
+          <t>2281169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122680</t>
+          <t>122867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>165887</t>
+          <t>165791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149545</t>
+          <t>152038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>194989</t>
+          <t>194003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284830</t>
+          <t>283238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344801</t>
+          <t>344793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315294</t>
+          <t>315390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>358501</t>
+          <t>358314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>263642</t>
+          <t>264628</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309086</t>
+          <t>306593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>595012</t>
+          <t>595020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654983</t>
+          <t>656575</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1443841</t>
+          <t>1451499</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1562086</t>
+          <t>1575620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1867351</t>
+          <t>1871305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1989208</t>
+          <t>1991580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3346668</t>
+          <t>3349829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3510402</t>
+          <t>3516048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1857696</t>
+          <t>1844162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1975941</t>
+          <t>1968283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1565022</t>
+          <t>1562650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1686879</t>
+          <t>1682925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3463610</t>
+          <t>3457964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3627344</t>
+          <t>3624183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,97%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>435415</t>
+          <t>433446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>488636</t>
+          <t>488599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>691749</t>
+          <t>694664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>751503</t>
+          <t>753638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1143347</t>
+          <t>1143882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1226659</t>
+          <t>1224535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,01%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265711</t>
+          <t>265748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>318932</t>
+          <t>320901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243157</t>
+          <t>241022</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302911</t>
+          <t>299996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522348</t>
+          <t>524472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>605660</t>
+          <t>605125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>676556</t>
+          <t>674921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>760400</t>
+          <t>762029</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>738587</t>
+          <t>739616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>827838</t>
+          <t>829901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1443068</t>
+          <t>1435426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1568363</t>
+          <t>1564096</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1315985</t>
+          <t>1314356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1399829</t>
+          <t>1401464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1160462</t>
+          <t>1158399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1249713</t>
+          <t>1248684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2496322</t>
+          <t>2500589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2621617</t>
+          <t>2629259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120848</t>
+          <t>120521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>164202</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162152</t>
+          <t>161382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206111</t>
+          <t>207210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>293864</t>
+          <t>295259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>356811</t>
+          <t>356452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>384699</t>
+          <t>382684</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426038</t>
+          <t>426365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>343029</t>
+          <t>341930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>386988</t>
+          <t>387758</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>739216</t>
+          <t>739575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>802163</t>
+          <t>800768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1253891</t>
+          <t>1267604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1375707</t>
+          <t>1378641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1625926</t>
+          <t>1627701</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1747467</t>
+          <t>1747954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2920983</t>
+          <t>2929660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3091655</t>
+          <t>3086588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2001911</t>
+          <t>1998977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2123727</t>
+          <t>2110014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1784633</t>
+          <t>1784146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1906174</t>
+          <t>1904399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3818063</t>
+          <t>3823130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3988735</t>
+          <t>3980058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>325914</t>
+          <t>324082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>368769</t>
+          <t>366462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>595169</t>
+          <t>595168</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>576138</t>
+          <t>575462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>613179</t>
+          <t>613727</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>915635</t>
+          <t>914318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>970290</t>
+          <t>970138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141627</t>
+          <t>143934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184482</t>
+          <t>186314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>150387</t>
+          <t>150388</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132377</t>
+          <t>131829</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>169418</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285661</t>
+          <t>285813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>340316</t>
+          <t>341633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>931903</t>
+          <t>936713</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1441493</t>
+          <t>1488324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>981273</t>
+          <t>981467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1450422</t>
+          <t>1421310</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1967549</t>
+          <t>1958992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2651310</t>
+          <t>2644860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>840053</t>
+          <t>793222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1349643</t>
+          <t>1344833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>781674</t>
+          <t>810786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1250823</t>
+          <t>1250629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1862332</t>
+          <t>1868782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2546093</t>
+          <t>2554650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>247130</t>
+          <t>246001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>300850</t>
+          <t>300571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>246648</t>
+          <t>247487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>289868</t>
+          <t>290458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>508386</t>
+          <t>506007</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>576204</t>
+          <t>577299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343611</t>
+          <t>343890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>397331</t>
+          <t>398460</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>367721</t>
+          <t>367131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>410941</t>
+          <t>410102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>725846</t>
+          <t>724751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>793664</t>
+          <t>796043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1559291</t>
+          <t>1565279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2097950</t>
+          <t>2116264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1845792</t>
+          <t>1857136</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2278946</t>
+          <t>2274429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3459552</t>
+          <t>3463289</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4134313</t>
+          <t>4136424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1338453</t>
+          <t>1320139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1877112</t>
+          <t>1871124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1356294</t>
+          <t>1360811</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1789448</t>
+          <t>1778104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2937330</t>
+          <t>2935219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3612091</t>
+          <t>3608354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>612280</t>
+          <t>614906</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>677562</t>
+          <t>673831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>966191</t>
+          <t>964668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1025466</t>
+          <t>1026594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1592478</t>
+          <t>1597746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1687401</t>
+          <t>1684110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354161</t>
+          <t>357892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419443</t>
+          <t>416817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289647</t>
+          <t>288519</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348922</t>
+          <t>350445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>659434</t>
+          <t>662725</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>754357</t>
+          <t>749089</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>531527</t>
+          <t>533371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>610934</t>
+          <t>610480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>683709</t>
+          <t>678597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>760617</t>
+          <t>760353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1234878</t>
+          <t>1237850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1347323</t>
+          <t>1350251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1082479</t>
+          <t>1082933</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1161886</t>
+          <t>1160042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>827056</t>
+          <t>827320</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>903964</t>
+          <t>909076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1933763</t>
+          <t>1930835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2046208</t>
+          <t>2043236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156720</t>
+          <t>159187</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202473</t>
+          <t>202838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187883</t>
+          <t>187727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>233104</t>
+          <t>232322</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>356904</t>
+          <t>359100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>420836</t>
+          <t>423736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>348935</t>
+          <t>348570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>394688</t>
+          <t>392221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243308</t>
+          <t>244090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288529</t>
+          <t>288685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>606984</t>
+          <t>604084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670916</t>
+          <t>668720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1334686</t>
+          <t>1334087</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1458948</t>
+          <t>1455877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1865497</t>
+          <t>1867507</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1982855</t>
+          <t>1984856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3242413</t>
+          <t>3242541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3406066</t>
+          <t>3411872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1817595</t>
+          <t>1820666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1941857</t>
+          <t>1942456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1396342</t>
+          <t>1394341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1513700</t>
+          <t>1511690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3249675</t>
+          <t>3243869</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3413328</t>
+          <t>3413200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>601221</t>
+          <t>598933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>659035</t>
+          <t>659447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>953302</t>
+          <t>948579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1019602</t>
+          <t>1018322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1570548</t>
+          <t>1569818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1661291</t>
+          <t>1657302</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>315608</t>
+          <t>315196</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373422</t>
+          <t>375710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>318195</t>
+          <t>319475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>384495</t>
+          <t>389218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>651149</t>
+          <t>655138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741892</t>
+          <t>742622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>688590</t>
+          <t>685840</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>778597</t>
+          <t>774212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725513</t>
+          <t>727556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>810901</t>
+          <t>810944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1440591</t>
+          <t>1435478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1562730</t>
+          <t>1557324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1185360</t>
+          <t>1189745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1275367</t>
+          <t>1278117</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>946902</t>
+          <t>946859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1032290</t>
+          <t>1030247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2159030</t>
+          <t>2164436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2281169</t>
+          <t>2286282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122867</t>
+          <t>123103</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>165791</t>
+          <t>165546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152038</t>
+          <t>148710</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>194003</t>
+          <t>193442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>283238</t>
+          <t>283391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344793</t>
+          <t>345770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315390</t>
+          <t>315635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>358314</t>
+          <t>358078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>264628</t>
+          <t>265189</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306593</t>
+          <t>309921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>595020</t>
+          <t>594043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656575</t>
+          <t>656422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1451499</t>
+          <t>1436590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1575620</t>
+          <t>1562202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1871305</t>
+          <t>1865451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1991580</t>
+          <t>1984915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3349829</t>
+          <t>3345803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3516048</t>
+          <t>3518654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1844162</t>
+          <t>1857580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1968283</t>
+          <t>1983192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1562650</t>
+          <t>1569315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1682925</t>
+          <t>1688779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3457964</t>
+          <t>3455358</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3624183</t>
+          <t>3628209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>433446</t>
+          <t>435784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>488599</t>
+          <t>489203</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>694664</t>
+          <t>692969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>753638</t>
+          <t>750073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1143882</t>
+          <t>1141243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1224535</t>
+          <t>1219500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265748</t>
+          <t>265144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>320901</t>
+          <t>318563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241022</t>
+          <t>244587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299996</t>
+          <t>301691</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524472</t>
+          <t>529507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>605125</t>
+          <t>607764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>674921</t>
+          <t>674469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>762029</t>
+          <t>765068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>739616</t>
+          <t>738405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>829901</t>
+          <t>829311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1435426</t>
+          <t>1434512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1564096</t>
+          <t>1566207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1314356</t>
+          <t>1311317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1401464</t>
+          <t>1401916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1158399</t>
+          <t>1158989</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1248684</t>
+          <t>1249895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2500589</t>
+          <t>2498478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2629259</t>
+          <t>2630173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120521</t>
+          <t>118098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164202</t>
+          <t>159436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161382</t>
+          <t>161443</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207210</t>
+          <t>207342</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295259</t>
+          <t>293106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>356452</t>
+          <t>355783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>382684</t>
+          <t>387450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426365</t>
+          <t>428788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>341930</t>
+          <t>341798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>387758</t>
+          <t>387697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>739575</t>
+          <t>740244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>800768</t>
+          <t>802921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,26%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1267604</t>
+          <t>1259077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1378641</t>
+          <t>1378645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1627701</t>
+          <t>1632621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1747954</t>
+          <t>1754400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2929660</t>
+          <t>2930164</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3086588</t>
+          <t>3088141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1998977</t>
+          <t>1998973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2110014</t>
+          <t>2118541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1784146</t>
+          <t>1777700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1904399</t>
+          <t>1899479</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3823130</t>
+          <t>3821577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3980058</t>
+          <t>3979554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,59%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>346564</t>
+          <t>376873</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>324082</t>
+          <t>353127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>366462</t>
+          <t>400105</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>595168</t>
+          <t>641750</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>575462</t>
+          <t>620967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>613727</t>
+          <t>661754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>941732</t>
+          <t>1018623</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>914318</t>
+          <t>986725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>970138</t>
+          <t>1048870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>163832</t>
+          <t>196716</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143934</t>
+          <t>173484</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186314</t>
+          <t>220462</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>150388</t>
+          <t>169722</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131829</t>
+          <t>149718</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>170094</t>
+          <t>190505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>314219</t>
+          <t>366438</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285813</t>
+          <t>336191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>341633</t>
+          <t>398336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1093457</t>
+          <t>921658</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>936713</t>
+          <t>865577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1488324</t>
+          <t>982550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1122737</t>
+          <t>1013901</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>981467</t>
+          <t>969832</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1421310</t>
+          <t>1055764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2216194</t>
+          <t>1935560</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1958992</t>
+          <t>1863730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2644860</t>
+          <t>2004835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1188089</t>
+          <t>1299309</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>793222</t>
+          <t>1238417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1344833</t>
+          <t>1355390</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1109359</t>
+          <t>1151519</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>810786</t>
+          <t>1109656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1250629</t>
+          <t>1195588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2297448</t>
+          <t>2450828</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1868782</t>
+          <t>2381553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2554650</t>
+          <t>2522658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>273520</t>
+          <t>297637</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>246001</t>
+          <t>269853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>300571</t>
+          <t>327084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>268271</t>
+          <t>305178</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>247487</t>
+          <t>278558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>290458</t>
+          <t>327112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>541791</t>
+          <t>602815</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>506007</t>
+          <t>567747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>577299</t>
+          <t>644020</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>370941</t>
+          <t>411497</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343890</t>
+          <t>382050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>398460</t>
+          <t>439281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>389318</t>
+          <t>426613</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>367131</t>
+          <t>404679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>410102</t>
+          <t>453233</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>760259</t>
+          <t>838110</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>724751</t>
+          <t>796905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>796043</t>
+          <t>873178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1713541</t>
+          <t>1596169</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1565279</t>
+          <t>1534399</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2116264</t>
+          <t>1657959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1986176</t>
+          <t>1960829</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1857136</t>
+          <t>1905289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2274429</t>
+          <t>2015972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3699717</t>
+          <t>3556998</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3463289</t>
+          <t>3480512</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4136424</t>
+          <t>3644232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>50,53%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1722862</t>
+          <t>1907522</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1320139</t>
+          <t>1845732</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1871124</t>
+          <t>1969292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1649064</t>
+          <t>1747854</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1360811</t>
+          <t>1692711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1778104</t>
+          <t>1803394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3371926</t>
+          <t>3655376</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2935219</t>
+          <t>3568142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3608354</t>
+          <t>3731862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
